--- a/artfynd/A 60590-2022 artfynd.xlsx
+++ b/artfynd/A 60590-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127699937</v>
+        <v>127699924</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730803</v>
+        <v>730805</v>
       </c>
       <c r="R2" t="n">
-        <v>7170923</v>
+        <v>7170832</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127699924</v>
+        <v>127699937</v>
       </c>
       <c r="B3" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730805</v>
+        <v>730803</v>
       </c>
       <c r="R3" t="n">
-        <v>7170832</v>
+        <v>7170923</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 60590-2022 artfynd.xlsx
+++ b/artfynd/A 60590-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127699924</v>
+        <v>127699937</v>
       </c>
       <c r="B2" t="n">
-        <v>78776</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730805</v>
+        <v>730803</v>
       </c>
       <c r="R2" t="n">
-        <v>7170832</v>
+        <v>7170923</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127699937</v>
+        <v>127699924</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>78778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730803</v>
+        <v>730805</v>
       </c>
       <c r="R3" t="n">
-        <v>7170923</v>
+        <v>7170832</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>127699925</v>
       </c>
       <c r="B4" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127699936</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127699938</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127699927</v>
       </c>
       <c r="B7" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127699904</v>
       </c>
       <c r="B8" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127699947</v>
       </c>
       <c r="B9" t="n">
-        <v>80156</v>
+        <v>80158</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127699928</v>
       </c>
       <c r="B10" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127699903</v>
       </c>
       <c r="B11" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127699934</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127699910</v>
       </c>
       <c r="B13" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127699926</v>
       </c>
       <c r="B14" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127699919</v>
       </c>
       <c r="B15" t="n">
-        <v>91803</v>
+        <v>91805</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 60590-2022 artfynd.xlsx
+++ b/artfynd/A 60590-2022 artfynd.xlsx
@@ -1745,7 +1745,7 @@
         <v>127699910</v>
       </c>
       <c r="B13" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127699919</v>
       </c>
       <c r="B15" t="n">
-        <v>91805</v>
+        <v>91811</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 60590-2022 artfynd.xlsx
+++ b/artfynd/A 60590-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127699937</v>
+        <v>127699924</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>78781</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730803</v>
+        <v>730805</v>
       </c>
       <c r="R2" t="n">
-        <v>7170923</v>
+        <v>7170832</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127699924</v>
+        <v>127699937</v>
       </c>
       <c r="B3" t="n">
-        <v>78778</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730805</v>
+        <v>730803</v>
       </c>
       <c r="R3" t="n">
-        <v>7170832</v>
+        <v>7170923</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>127699925</v>
       </c>
       <c r="B4" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127699936</v>
+        <v>127699938</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730884</v>
+        <v>730740</v>
       </c>
       <c r="R5" t="n">
-        <v>7170882</v>
+        <v>7170912</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127699938</v>
+        <v>127699936</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730740</v>
+        <v>730884</v>
       </c>
       <c r="R6" t="n">
-        <v>7170912</v>
+        <v>7170882</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>127699927</v>
       </c>
       <c r="B7" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127699904</v>
       </c>
       <c r="B8" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127699947</v>
+        <v>127699928</v>
       </c>
       <c r="B9" t="n">
-        <v>80158</v>
+        <v>78781</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730887</v>
+        <v>730734</v>
       </c>
       <c r="R9" t="n">
-        <v>7170898</v>
+        <v>7170922</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127699928</v>
+        <v>127699947</v>
       </c>
       <c r="B10" t="n">
-        <v>78778</v>
+        <v>80161</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730734</v>
+        <v>730887</v>
       </c>
       <c r="R10" t="n">
-        <v>7170922</v>
+        <v>7170898</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
         <v>127699903</v>
       </c>
       <c r="B11" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127699934</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127699910</v>
       </c>
       <c r="B13" t="n">
-        <v>97339</v>
+        <v>97342</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127699926</v>
       </c>
       <c r="B14" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127699919</v>
       </c>
       <c r="B15" t="n">
-        <v>91811</v>
+        <v>91814</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 60590-2022 artfynd.xlsx
+++ b/artfynd/A 60590-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127699924</v>
+        <v>127699937</v>
       </c>
       <c r="B2" t="n">
-        <v>78781</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730805</v>
+        <v>730803</v>
       </c>
       <c r="R2" t="n">
-        <v>7170832</v>
+        <v>7170923</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127699937</v>
+        <v>127699924</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>78787</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730803</v>
+        <v>730805</v>
       </c>
       <c r="R3" t="n">
-        <v>7170923</v>
+        <v>7170832</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>127699925</v>
       </c>
       <c r="B4" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127699938</v>
+        <v>127699936</v>
       </c>
       <c r="B5" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730740</v>
+        <v>730884</v>
       </c>
       <c r="R5" t="n">
-        <v>7170912</v>
+        <v>7170882</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127699936</v>
+        <v>127699938</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730884</v>
+        <v>730740</v>
       </c>
       <c r="R6" t="n">
-        <v>7170882</v>
+        <v>7170912</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>127699927</v>
       </c>
       <c r="B7" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127699904</v>
       </c>
       <c r="B8" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127699928</v>
+        <v>127699947</v>
       </c>
       <c r="B9" t="n">
-        <v>78781</v>
+        <v>80167</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730734</v>
+        <v>730887</v>
       </c>
       <c r="R9" t="n">
-        <v>7170922</v>
+        <v>7170898</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127699947</v>
+        <v>127699928</v>
       </c>
       <c r="B10" t="n">
-        <v>80161</v>
+        <v>78787</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730887</v>
+        <v>730734</v>
       </c>
       <c r="R10" t="n">
-        <v>7170898</v>
+        <v>7170922</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
         <v>127699903</v>
       </c>
       <c r="B11" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127699934</v>
       </c>
       <c r="B12" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127699910</v>
       </c>
       <c r="B13" t="n">
-        <v>97342</v>
+        <v>97350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127699926</v>
       </c>
       <c r="B14" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127699919</v>
       </c>
       <c r="B15" t="n">
-        <v>91814</v>
+        <v>91822</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 60590-2022 artfynd.xlsx
+++ b/artfynd/A 60590-2022 artfynd.xlsx
@@ -1745,7 +1745,7 @@
         <v>127699910</v>
       </c>
       <c r="B13" t="n">
-        <v>97350</v>
+        <v>97351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127699919</v>
       </c>
       <c r="B15" t="n">
-        <v>91822</v>
+        <v>91823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 60590-2022 artfynd.xlsx
+++ b/artfynd/A 60590-2022 artfynd.xlsx
@@ -1745,7 +1745,7 @@
         <v>127699910</v>
       </c>
       <c r="B13" t="n">
-        <v>97351</v>
+        <v>97352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127699919</v>
       </c>
       <c r="B15" t="n">
-        <v>91823</v>
+        <v>91824</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 60590-2022 artfynd.xlsx
+++ b/artfynd/A 60590-2022 artfynd.xlsx
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127699936</v>
+        <v>127699938</v>
       </c>
       <c r="B5" t="n">
         <v>79029</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730884</v>
+        <v>730740</v>
       </c>
       <c r="R5" t="n">
-        <v>7170882</v>
+        <v>7170912</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127699938</v>
+        <v>127699936</v>
       </c>
       <c r="B6" t="n">
         <v>79029</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730740</v>
+        <v>730884</v>
       </c>
       <c r="R6" t="n">
-        <v>7170912</v>
+        <v>7170882</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
         <v>127699910</v>
       </c>
       <c r="B13" t="n">
-        <v>97352</v>
+        <v>97353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127699919</v>
       </c>
       <c r="B15" t="n">
-        <v>91824</v>
+        <v>91825</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 60590-2022 artfynd.xlsx
+++ b/artfynd/A 60590-2022 artfynd.xlsx
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127699938</v>
+        <v>127699936</v>
       </c>
       <c r="B5" t="n">
         <v>79029</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730740</v>
+        <v>730884</v>
       </c>
       <c r="R5" t="n">
-        <v>7170912</v>
+        <v>7170882</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127699936</v>
+        <v>127699938</v>
       </c>
       <c r="B6" t="n">
         <v>79029</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730884</v>
+        <v>730740</v>
       </c>
       <c r="R6" t="n">
-        <v>7170882</v>
+        <v>7170912</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127699947</v>
+        <v>127699928</v>
       </c>
       <c r="B9" t="n">
-        <v>80167</v>
+        <v>78787</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730887</v>
+        <v>730734</v>
       </c>
       <c r="R9" t="n">
-        <v>7170898</v>
+        <v>7170922</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127699928</v>
+        <v>127699947</v>
       </c>
       <c r="B10" t="n">
-        <v>78787</v>
+        <v>80167</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730734</v>
+        <v>730887</v>
       </c>
       <c r="R10" t="n">
-        <v>7170922</v>
+        <v>7170898</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 60590-2022 artfynd.xlsx
+++ b/artfynd/A 60590-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127699937</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127699924</v>
       </c>
       <c r="B3" t="n">
-        <v>78787</v>
+        <v>78790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127699925</v>
       </c>
       <c r="B4" t="n">
-        <v>78787</v>
+        <v>78790</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127699936</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127699938</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127699927</v>
       </c>
       <c r="B7" t="n">
-        <v>78787</v>
+        <v>78790</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127699904</v>
       </c>
       <c r="B8" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127699928</v>
+        <v>127699947</v>
       </c>
       <c r="B9" t="n">
-        <v>78787</v>
+        <v>80170</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730734</v>
+        <v>730887</v>
       </c>
       <c r="R9" t="n">
-        <v>7170922</v>
+        <v>7170898</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127699947</v>
+        <v>127699928</v>
       </c>
       <c r="B10" t="n">
-        <v>80167</v>
+        <v>78790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730887</v>
+        <v>730734</v>
       </c>
       <c r="R10" t="n">
-        <v>7170898</v>
+        <v>7170922</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
         <v>127699903</v>
       </c>
       <c r="B11" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127699934</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127699910</v>
       </c>
       <c r="B13" t="n">
-        <v>97353</v>
+        <v>97361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127699926</v>
       </c>
       <c r="B14" t="n">
-        <v>78787</v>
+        <v>78790</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127699919</v>
       </c>
       <c r="B15" t="n">
-        <v>91825</v>
+        <v>91833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 60590-2022 artfynd.xlsx
+++ b/artfynd/A 60590-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127699937</v>
       </c>
       <c r="B2" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127699924</v>
       </c>
       <c r="B3" t="n">
-        <v>78790</v>
+        <v>78801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127699925</v>
       </c>
       <c r="B4" t="n">
-        <v>78790</v>
+        <v>78801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127699936</v>
       </c>
       <c r="B5" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127699938</v>
       </c>
       <c r="B6" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127699927</v>
       </c>
       <c r="B7" t="n">
-        <v>78790</v>
+        <v>78801</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>127699904</v>
       </c>
       <c r="B8" t="n">
-        <v>79650</v>
+        <v>79661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>127699947</v>
       </c>
       <c r="B9" t="n">
-        <v>80170</v>
+        <v>80181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>127699928</v>
       </c>
       <c r="B10" t="n">
-        <v>78790</v>
+        <v>78801</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>127699903</v>
       </c>
       <c r="B11" t="n">
-        <v>79650</v>
+        <v>79661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>127699934</v>
       </c>
       <c r="B12" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>127699910</v>
       </c>
       <c r="B13" t="n">
-        <v>97361</v>
+        <v>97373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>127699926</v>
       </c>
       <c r="B14" t="n">
-        <v>78790</v>
+        <v>78801</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>127699919</v>
       </c>
       <c r="B15" t="n">
-        <v>91833</v>
+        <v>91844</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 60590-2022 artfynd.xlsx
+++ b/artfynd/A 60590-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127699937</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,14 +768,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>127699924</v>
       </c>
       <c r="B3" t="n">
-        <v>78801</v>
+        <v>78877</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -865,14 +869,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>127699925</v>
       </c>
       <c r="B4" t="n">
-        <v>78801</v>
+        <v>78877</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,14 +970,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>127699936</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,14 +1071,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>127699938</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,14 +1172,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>127699927</v>
       </c>
       <c r="B7" t="n">
-        <v>78801</v>
+        <v>78877</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1253,14 +1273,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
         <v>127699904</v>
       </c>
       <c r="B8" t="n">
-        <v>79661</v>
+        <v>79739</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1350,14 +1374,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>127699947</v>
       </c>
       <c r="B9" t="n">
-        <v>80181</v>
+        <v>80260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1447,14 +1475,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>127699928</v>
       </c>
       <c r="B10" t="n">
-        <v>78801</v>
+        <v>78877</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,14 +1576,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>127699903</v>
       </c>
       <c r="B11" t="n">
-        <v>79661</v>
+        <v>79739</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,14 +1677,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>127699934</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,14 +1778,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>127699910</v>
       </c>
       <c r="B13" t="n">
-        <v>97373</v>
+        <v>97509</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1835,14 +1879,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>127699926</v>
       </c>
       <c r="B14" t="n">
-        <v>78801</v>
+        <v>78877</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1932,14 +1980,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>127699919</v>
       </c>
       <c r="B15" t="n">
-        <v>91844</v>
+        <v>91977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2029,7 +2081,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60590-2022 artfynd.xlsx
+++ b/artfynd/A 60590-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127699937</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127699924</v>
       </c>
       <c r="B3" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127699925</v>
       </c>
       <c r="B4" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127699936</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127699938</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127699927</v>
       </c>
       <c r="B7" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127699904</v>
       </c>
       <c r="B8" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127699947</v>
       </c>
       <c r="B9" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127699928</v>
       </c>
       <c r="B10" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127699903</v>
       </c>
       <c r="B11" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>127699934</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>127699910</v>
       </c>
       <c r="B13" t="n">
-        <v>97509</v>
+        <v>97513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>127699926</v>
       </c>
       <c r="B14" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>127699919</v>
       </c>
       <c r="B15" t="n">
-        <v>91977</v>
+        <v>91981</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 60590-2022 artfynd.xlsx
+++ b/artfynd/A 60590-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127699937</v>
       </c>
       <c r="B2" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127699924</v>
       </c>
       <c r="B3" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127699925</v>
       </c>
       <c r="B4" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127699936</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127699938</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127699927</v>
       </c>
       <c r="B7" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127699904</v>
       </c>
       <c r="B8" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127699947</v>
       </c>
       <c r="B9" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127699928</v>
       </c>
       <c r="B10" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127699903</v>
       </c>
       <c r="B11" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>127699934</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>127699910</v>
       </c>
       <c r="B13" t="n">
-        <v>97513</v>
+        <v>97520</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>127699926</v>
       </c>
       <c r="B14" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>127699919</v>
       </c>
       <c r="B15" t="n">
-        <v>91981</v>
+        <v>91986</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 60590-2022 artfynd.xlsx
+++ b/artfynd/A 60590-2022 artfynd.xlsx
@@ -1789,7 +1789,7 @@
         <v>127699910</v>
       </c>
       <c r="B13" t="n">
-        <v>97528</v>
+        <v>97533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>127699919</v>
       </c>
       <c r="B15" t="n">
-        <v>91994</v>
+        <v>91997</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 60590-2022 artfynd.xlsx
+++ b/artfynd/A 60590-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127699937</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127699924</v>
       </c>
       <c r="B3" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127699925</v>
       </c>
       <c r="B4" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127699936</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127699938</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127699927</v>
       </c>
       <c r="B7" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127699904</v>
       </c>
       <c r="B8" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127699947</v>
       </c>
       <c r="B9" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127699928</v>
       </c>
       <c r="B10" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127699903</v>
       </c>
       <c r="B11" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>127699934</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>127699910</v>
       </c>
       <c r="B13" t="n">
-        <v>97533</v>
+        <v>97536</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>127699926</v>
       </c>
       <c r="B14" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>127699919</v>
       </c>
       <c r="B15" t="n">
-        <v>91997</v>
+        <v>92000</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 60590-2022 artfynd.xlsx
+++ b/artfynd/A 60590-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127699937</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127699924</v>
       </c>
       <c r="B3" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127699925</v>
       </c>
       <c r="B4" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127699936</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127699938</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127699927</v>
       </c>
       <c r="B7" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127699904</v>
       </c>
       <c r="B8" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127699947</v>
       </c>
       <c r="B9" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127699928</v>
       </c>
       <c r="B10" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127699903</v>
       </c>
       <c r="B11" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>127699934</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>127699910</v>
       </c>
       <c r="B13" t="n">
-        <v>97536</v>
+        <v>97546</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>127699926</v>
       </c>
       <c r="B14" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>127699919</v>
       </c>
       <c r="B15" t="n">
-        <v>92000</v>
+        <v>92007</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 60590-2022 artfynd.xlsx
+++ b/artfynd/A 60590-2022 artfynd.xlsx
@@ -1789,7 +1789,7 @@
         <v>127699910</v>
       </c>
       <c r="B13" t="n">
-        <v>97546</v>
+        <v>97553</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>127699919</v>
       </c>
       <c r="B15" t="n">
-        <v>92007</v>
+        <v>92014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 60590-2022 artfynd.xlsx
+++ b/artfynd/A 60590-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127699937</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127699924</v>
       </c>
       <c r="B3" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127699925</v>
       </c>
       <c r="B4" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127699936</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127699938</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127699927</v>
       </c>
       <c r="B7" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127699904</v>
       </c>
       <c r="B8" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127699947</v>
       </c>
       <c r="B9" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127699928</v>
       </c>
       <c r="B10" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127699903</v>
       </c>
       <c r="B11" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>127699934</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>127699910</v>
       </c>
       <c r="B13" t="n">
-        <v>97553</v>
+        <v>97555</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>127699926</v>
       </c>
       <c r="B14" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>127699919</v>
       </c>
       <c r="B15" t="n">
-        <v>92014</v>
+        <v>92016</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 60590-2022 artfynd.xlsx
+++ b/artfynd/A 60590-2022 artfynd.xlsx
@@ -1789,7 +1789,7 @@
         <v>127699910</v>
       </c>
       <c r="B13" t="n">
-        <v>97555</v>
+        <v>97581</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>127699919</v>
       </c>
       <c r="B15" t="n">
-        <v>92016</v>
+        <v>92022</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 60590-2022 artfynd.xlsx
+++ b/artfynd/A 60590-2022 artfynd.xlsx
@@ -1789,7 +1789,7 @@
         <v>127699910</v>
       </c>
       <c r="B13" t="n">
-        <v>97581</v>
+        <v>97582</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>127699919</v>
       </c>
       <c r="B15" t="n">
-        <v>92022</v>
+        <v>92023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 60590-2022 artfynd.xlsx
+++ b/artfynd/A 60590-2022 artfynd.xlsx
@@ -1789,7 +1789,7 @@
         <v>127699910</v>
       </c>
       <c r="B13" t="n">
-        <v>97582</v>
+        <v>97583</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 60590-2022 artfynd.xlsx
+++ b/artfynd/A 60590-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127699937</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127699924</v>
       </c>
       <c r="B3" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127699925</v>
       </c>
       <c r="B4" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127699936</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127699938</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127699927</v>
       </c>
       <c r="B7" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127699904</v>
       </c>
       <c r="B8" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127699947</v>
       </c>
       <c r="B9" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127699928</v>
       </c>
       <c r="B10" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127699903</v>
       </c>
       <c r="B11" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>127699934</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>127699910</v>
       </c>
       <c r="B13" t="n">
-        <v>97583</v>
+        <v>97587</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>127699926</v>
       </c>
       <c r="B14" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>127699919</v>
       </c>
       <c r="B15" t="n">
-        <v>92023</v>
+        <v>92026</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 60590-2022 artfynd.xlsx
+++ b/artfynd/A 60590-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127699937</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>127699924</v>
       </c>
       <c r="B3" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>127699925</v>
       </c>
       <c r="B4" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>127699936</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127699938</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>127699927</v>
       </c>
       <c r="B7" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>127699904</v>
       </c>
       <c r="B8" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>127699947</v>
       </c>
       <c r="B9" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>127699928</v>
       </c>
       <c r="B10" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>127699903</v>
       </c>
       <c r="B11" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>127699934</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>127699910</v>
       </c>
       <c r="B13" t="n">
-        <v>97587</v>
+        <v>97589</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>127699926</v>
       </c>
       <c r="B14" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>127699919</v>
       </c>
       <c r="B15" t="n">
-        <v>92026</v>
+        <v>92028</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 60590-2022 artfynd.xlsx
+++ b/artfynd/A 60590-2022 artfynd.xlsx
@@ -1789,7 +1789,7 @@
         <v>127699910</v>
       </c>
       <c r="B13" t="n">
-        <v>97589</v>
+        <v>97593</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>127699919</v>
       </c>
       <c r="B15" t="n">
-        <v>92028</v>
+        <v>92032</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
